--- a/salidas/empresas/BSX.xlsx
+++ b/salidas/empresas/BSX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1324,7 +1336,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1349,7 +1361,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1374,7 +1386,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1399,7 +1411,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1424,7 +1436,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1449,7 +1461,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1474,7 +1486,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1499,7 +1511,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1524,7 +1536,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1549,7 +1561,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1574,7 +1586,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1599,7 +1611,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1624,7 +1636,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1649,7 +1661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1674,7 +1686,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1724,7 +1736,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1749,7 +1761,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1776,7 +1788,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1803,7 +1815,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1830,7 +1842,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1859,7 +1871,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1888,7 +1900,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1917,7 +1929,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1946,7 +1958,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1975,7 +1987,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2004,7 +2016,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2033,7 +2045,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2062,7 +2074,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2091,7 +2103,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2120,7 +2132,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2149,7 +2161,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2178,7 +2190,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2207,7 +2219,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2236,7 +2248,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2265,7 +2277,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2292,7 +2304,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2319,7 +2331,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2346,7 +2358,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2373,7 +2385,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2400,7 +2412,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2427,7 +2439,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2454,7 +2466,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2481,7 +2493,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2508,7 +2520,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2535,7 +2547,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2562,7 +2574,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2589,7 +2601,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2616,7 +2628,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2643,7 +2655,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2670,7 +2682,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2697,7 +2709,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2724,7 +2736,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2751,7 +2763,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2778,7 +2790,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2805,7 +2817,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2832,7 +2844,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2861,7 +2873,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2890,7 +2902,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2919,7 +2931,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -2948,7 +2960,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -2977,7 +2989,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3006,7 +3018,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3035,7 +3047,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3064,7 +3076,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3093,7 +3105,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3120,7 +3132,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3147,7 +3159,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3174,7 +3186,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3201,7 +3213,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3228,7 +3240,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3255,7 +3267,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3282,7 +3294,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3309,7 +3321,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3336,7 +3348,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3363,7 +3375,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3390,7 +3402,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3417,7 +3429,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3444,7 +3456,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3471,7 +3483,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3498,7 +3510,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3525,7 +3537,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3552,7 +3564,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3579,7 +3591,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3606,7 +3618,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3633,7 +3645,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3660,7 +3672,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3689,7 +3701,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3718,7 +3730,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3747,7 +3759,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3776,7 +3788,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3805,7 +3817,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3834,7 +3846,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3863,7 +3875,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3892,7 +3904,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3921,7 +3933,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -3950,7 +3962,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -3979,7 +3991,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4008,7 +4020,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4037,7 +4049,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4066,7 +4078,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4095,7 +4107,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4124,7 +4136,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4153,7 +4165,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4182,7 +4194,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4211,7 +4223,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4240,7 +4252,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4269,7 +4281,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4298,7 +4310,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4327,7 +4339,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4356,7 +4368,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4385,7 +4397,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4414,7 +4426,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4443,7 +4455,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4472,7 +4484,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4501,7 +4513,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4530,7 +4542,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4559,7 +4571,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4588,7 +4600,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4617,7 +4629,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4646,7 +4658,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4675,7 +4687,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4704,7 +4716,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4733,7 +4745,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4762,7 +4774,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4791,7 +4803,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4820,7 +4832,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4849,7 +4861,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4878,7 +4890,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -4907,7 +4919,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4936,7 +4948,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -4965,7 +4977,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -4994,7 +5006,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5023,7 +5035,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5052,7 +5064,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5081,7 +5093,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5110,7 +5122,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5139,7 +5151,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5166,7 +5178,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5193,7 +5205,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5220,7 +5232,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5249,7 +5261,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5278,7 +5290,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5307,7 +5319,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5336,7 +5348,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5365,7 +5377,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5394,7 +5406,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5423,7 +5435,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5452,7 +5464,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5481,7 +5493,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5510,7 +5522,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5539,7 +5551,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5568,7 +5580,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5597,7 +5609,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5626,7 +5638,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5655,7 +5667,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5684,7 +5696,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5713,7 +5725,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5742,7 +5754,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5771,7 +5783,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5800,7 +5812,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5829,7 +5841,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5858,7 +5870,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5887,7 +5899,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -5916,7 +5928,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -5945,7 +5957,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -5974,7 +5986,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6003,7 +6015,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6032,7 +6044,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6061,7 +6073,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6090,7 +6102,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6119,7 +6131,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6148,7 +6160,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6177,7 +6189,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6206,7 +6218,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6235,7 +6247,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6264,7 +6276,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6293,7 +6305,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6322,7 +6334,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6351,7 +6363,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6380,7 +6392,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6409,7 +6421,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6438,7 +6450,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6467,7 +6479,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6496,7 +6508,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6525,7 +6537,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6554,7 +6566,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6583,7 +6595,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6612,7 +6624,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6641,7 +6653,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6670,7 +6682,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6699,7 +6711,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6728,7 +6740,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6757,7 +6769,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6786,7 +6798,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6815,7 +6827,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6844,7 +6856,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6873,7 +6885,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6902,7 +6914,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6931,7 +6943,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6960,7 +6972,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6989,7 +7001,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7018,7 +7030,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7047,7 +7059,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7076,32 +7088,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>44.61999893188477</v>
+        <v>44.68000030517578</v>
       </c>
       <c r="C250" t="n">
-        <v>44.61999893188477</v>
+        <v>44.68000030517578</v>
       </c>
       <c r="D250" t="n">
-        <v>352406500</v>
+        <v>369702700</v>
       </c>
       <c r="E250" t="n">
         <v>2.470000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>18.0647768954999</v>
+        <v>18.08906894946388</v>
       </c>
       <c r="G250" t="n">
         <v>1449229526</v>
       </c>
       <c r="H250" t="n">
-        <v>64664619902.17587</v>
+        <v>64751575663.94975</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2431681756944828</v>
+        <v>0.2551029311557098</v>
       </c>
     </row>
   </sheetData>
@@ -7133,75 +7145,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7237,13 +7249,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7279,13 +7291,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7321,13 +7333,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7363,13 +7375,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7438,7 +7450,7 @@
       <c r="I7" t="n">
         <v>-0.6799999999999999</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K7" t="n">
@@ -7451,13 +7463,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7484,7 +7496,7 @@
       <c r="I8" t="n">
         <v>-1.72</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K8" t="n">
@@ -7497,13 +7509,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7530,7 +7542,7 @@
       <c r="I9" t="n">
         <v>-1.76</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K9" t="n">
@@ -7543,13 +7555,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7576,7 +7588,7 @@
       <c r="I10" t="n">
         <v>-1.58</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K10" t="n">
@@ -7589,13 +7601,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7622,7 +7634,7 @@
       <c r="I11" t="n">
         <v>-0.7200000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="K11" t="n">
@@ -7635,13 +7647,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7668,7 +7680,7 @@
       <c r="I12" t="n">
         <v>0.36</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="K12" t="n">
@@ -7681,13 +7693,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7714,7 +7726,7 @@
       <c r="I13" t="n">
         <v>0.4</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="K13" t="n">
@@ -7727,13 +7739,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7760,7 +7772,7 @@
       <c r="I14" t="n">
         <v>0.37</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="K14" t="n">
@@ -7773,13 +7785,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7806,7 +7818,7 @@
       <c r="I15" t="n">
         <v>0.29</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="K15" t="n">
@@ -7819,13 +7831,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7852,7 +7864,7 @@
       <c r="I16" t="n">
         <v>0.34</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="K16" t="n">
@@ -7865,13 +7877,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7898,7 +7910,7 @@
       <c r="I17" t="n">
         <v>-2.27</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="K17" t="n">
@@ -7911,13 +7923,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7944,7 +7956,7 @@
       <c r="I18" t="n">
         <v>-2.839999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="K18" t="n">
@@ -7957,13 +7969,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7990,7 +8002,7 @@
       <c r="I19" t="n">
         <v>-2.89</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="K19" t="n">
@@ -8003,13 +8015,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8036,7 +8048,7 @@
       <c r="I20" t="n">
         <v>-3.23</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="K20" t="n">
@@ -8049,13 +8061,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8082,7 +8094,7 @@
       <c r="I21" t="n">
         <v>-0.62</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="K21" t="n">
@@ -8095,13 +8107,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8128,7 +8140,7 @@
       <c r="I22" t="n">
         <v>-0.14</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K22" t="n">
@@ -8141,13 +8153,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8174,7 +8186,7 @@
       <c r="I23" t="n">
         <v>-0.08999999999999955</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="K23" t="n">
@@ -8187,13 +8199,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8220,7 +8232,7 @@
       <c r="I24" t="n">
         <v>0.2700000000000005</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K24" t="n">
@@ -8233,13 +8245,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8266,7 +8278,7 @@
       <c r="I25" t="n">
         <v>0.1700000000000005</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="K25" t="n">
@@ -8279,13 +8291,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8312,7 +8324,7 @@
       <c r="I26" t="n">
         <v>0.2000000000000005</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="K26" t="n">
@@ -8325,13 +8337,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8358,7 +8370,7 @@
       <c r="I27" t="n">
         <v>-0.08999999999999955</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K27" t="n">
@@ -8371,13 +8383,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8404,7 +8416,7 @@
       <c r="I28" t="n">
         <v>-0.1899999999999996</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="K28" t="n">
@@ -8417,13 +8429,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="I29" t="n">
         <v>-0.1099999999999996</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K29" t="n">
@@ -8463,13 +8475,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8496,7 +8508,7 @@
       <c r="I30" t="n">
         <v>-0.2899999999999996</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K30" t="n">
@@ -8509,13 +8521,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8542,7 +8554,7 @@
       <c r="I31" t="n">
         <v>-0.1799999999999995</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K31" t="n">
@@ -8555,13 +8567,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8588,7 +8600,7 @@
       <c r="I32" t="n">
         <v>-0.02999999999999953</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="K32" t="n">
@@ -8601,13 +8613,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8634,7 +8646,7 @@
       <c r="I33" t="n">
         <v>-0.2599999999999995</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="K33" t="n">
@@ -8647,13 +8659,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8680,7 +8692,7 @@
       <c r="I34" t="n">
         <v>0.06000000000000047</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K34" t="n">
@@ -8693,13 +8705,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8726,7 +8738,7 @@
       <c r="I35" t="n">
         <v>0.2500000000000004</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8739,13 +8751,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8772,7 +8784,7 @@
       <c r="I36" t="n">
         <v>0.3100000000000004</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="K36" t="n">
@@ -8785,13 +8797,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8818,7 +8830,7 @@
       <c r="I37" t="n">
         <v>0.5700000000000004</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K37" t="n">
@@ -8831,13 +8843,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8864,7 +8876,7 @@
       <c r="I38" t="n">
         <v>0.6000000000000004</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K38" t="n">
@@ -8877,13 +8889,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8910,7 +8922,7 @@
       <c r="I39" t="n">
         <v>0.08000000000000046</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="K39" t="n">
@@ -8923,13 +8935,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8956,7 +8968,7 @@
       <c r="I40" t="n">
         <v>0.08000000000000043</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K40" t="n">
@@ -8969,13 +8981,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9002,7 +9014,7 @@
       <c r="I41" t="n">
         <v>0.3700000000000004</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="K41" t="n">
@@ -9015,13 +9027,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43402</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9048,7 +9060,7 @@
       <c r="I42" t="n">
         <v>0.4800000000000004</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43402</v>
       </c>
       <c r="K42" t="n">
@@ -9061,13 +9073,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9094,7 +9106,7 @@
       <c r="I43" t="n">
         <v>1.19</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="K43" t="n">
@@ -9107,13 +9119,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43584</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9140,7 +9152,7 @@
       <c r="I44" t="n">
         <v>1.28</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43584</v>
       </c>
       <c r="K44" t="n">
@@ -9153,13 +9165,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9186,7 +9198,7 @@
       <c r="I45" t="n">
         <v>0.9900000000000004</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="K45" t="n">
@@ -9199,13 +9211,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9232,7 +9244,7 @@
       <c r="I46" t="n">
         <v>0.7700000000000004</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K46" t="n">
@@ -9245,13 +9257,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9278,7 +9290,7 @@
       <c r="I47" t="n">
         <v>3.330000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="K47" t="n">
@@ -9291,13 +9303,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9324,7 +9336,7 @@
       <c r="I48" t="n">
         <v>3.04</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K48" t="n">
@@ -9337,13 +9349,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9370,7 +9382,7 @@
       <c r="I49" t="n">
         <v>2.82</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K49" t="n">
@@ -9383,13 +9395,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9416,7 +9428,7 @@
       <c r="I50" t="n">
         <v>2.61</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K50" t="n">
@@ -9429,13 +9441,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9462,7 +9474,7 @@
       <c r="I51" t="n">
         <v>-0.07999999999999954</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K51" t="n">
@@ -9475,13 +9487,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9508,7 +9520,7 @@
       <c r="I52" t="n">
         <v>0.1400000000000005</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K52" t="n">
@@ -9521,13 +9533,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9554,7 +9566,7 @@
       <c r="I53" t="n">
         <v>0.3700000000000004</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="K53" t="n">
@@ -9567,13 +9579,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9600,7 +9612,7 @@
       <c r="I54" t="n">
         <v>0.7700000000000005</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K54" t="n">
@@ -9613,13 +9625,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9646,7 +9658,7 @@
       <c r="I55" t="n">
         <v>0.6900000000000004</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="K55" t="n">
@@ -9659,13 +9671,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9692,7 +9704,7 @@
       <c r="I56" t="n">
         <v>0.5300000000000005</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K56" t="n">
@@ -9705,13 +9717,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9738,7 +9750,7 @@
       <c r="I57" t="n">
         <v>0.5800000000000004</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K57" t="n">
@@ -9751,13 +9763,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9784,7 +9796,7 @@
       <c r="I58" t="n">
         <v>0.4200000000000004</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K58" t="n">
@@ -9797,13 +9809,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9830,7 +9842,7 @@
       <c r="I59" t="n">
         <v>0.4500000000000005</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9843,13 +9855,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9876,7 +9888,7 @@
       <c r="I60" t="n">
         <v>0.5900000000000005</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K60" t="n">
@@ -9889,13 +9901,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9922,7 +9934,7 @@
       <c r="I61" t="n">
         <v>0.6000000000000004</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K61" t="n">
@@ -9935,13 +9947,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9968,7 +9980,7 @@
       <c r="I62" t="n">
         <v>0.8200000000000005</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="K62" t="n">
@@ -9981,13 +9993,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10014,7 +10026,7 @@
       <c r="I63" t="n">
         <v>1.070000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K63" t="n">
@@ -10027,13 +10039,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10060,7 +10072,7 @@
       <c r="I64" t="n">
         <v>1.190000000000001</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10073,13 +10085,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10106,7 +10118,7 @@
       <c r="I65" t="n">
         <v>1.230000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K65" t="n">
@@ -10119,13 +10131,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10152,7 +10164,7 @@
       <c r="I66" t="n">
         <v>1.210000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="K66" t="n">
@@ -10165,13 +10177,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10198,7 +10210,7 @@
       <c r="I67" t="n">
         <v>1.25</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="K67" t="n">
@@ -10211,13 +10223,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10244,7 +10256,7 @@
       <c r="I68" t="n">
         <v>1.37</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K68" t="n">
@@ -10257,13 +10269,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10290,7 +10302,7 @@
       <c r="I69" t="n">
         <v>1.68</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K69" t="n">
@@ -10303,13 +10315,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10336,7 +10348,7 @@
       <c r="I70" t="n">
         <v>1.87</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="K70" t="n">
@@ -10349,13 +10361,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10382,7 +10394,7 @@
       <c r="I71" t="n">
         <v>1.94</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="K71" t="n">
@@ -10395,13 +10407,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10428,7 +10440,7 @@
       <c r="I72" t="n">
         <v>2.390000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K72" t="n">
@@ -10441,13 +10453,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10474,7 +10486,7 @@
       <c r="I73" t="n">
         <v>2.470000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="K73" t="n">
@@ -10511,52 +10523,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40031</v>
       </c>
       <c r="C2" t="n">
@@ -10585,10 +10597,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40123</v>
       </c>
       <c r="C3" t="n">
@@ -10617,10 +10629,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10649,10 +10661,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40304</v>
       </c>
       <c r="C5" t="n">
@@ -10681,10 +10693,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40395</v>
       </c>
       <c r="C6" t="n">
@@ -10713,10 +10725,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40487</v>
       </c>
       <c r="C7" t="n">
@@ -10745,10 +10757,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="C8" t="n">
@@ -10777,10 +10789,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40668</v>
       </c>
       <c r="C9" t="n">
@@ -10809,10 +10821,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40760</v>
       </c>
       <c r="C10" t="n">
@@ -10841,10 +10853,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40855</v>
       </c>
       <c r="C11" t="n">
@@ -10873,10 +10885,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40956</v>
       </c>
       <c r="C12" t="n">
@@ -10905,10 +10917,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41032</v>
       </c>
       <c r="C13" t="n">
@@ -10937,10 +10949,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41128</v>
       </c>
       <c r="C14" t="n">
@@ -10969,10 +10981,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41219</v>
       </c>
       <c r="C15" t="n">
@@ -11001,10 +11013,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41327</v>
       </c>
       <c r="C16" t="n">
@@ -11033,10 +11045,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41401</v>
       </c>
       <c r="C17" t="n">
@@ -11065,10 +11077,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41493</v>
       </c>
       <c r="C18" t="n">
@@ -11097,10 +11109,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -11129,10 +11141,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41696</v>
       </c>
       <c r="C20" t="n">
@@ -11161,10 +11173,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C21" t="n">
@@ -11193,10 +11205,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41857</v>
       </c>
       <c r="C22" t="n">
@@ -11225,10 +11237,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41948</v>
       </c>
       <c r="C23" t="n">
@@ -11257,10 +11269,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C24" t="n">
@@ -11289,10 +11301,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42130</v>
       </c>
       <c r="C25" t="n">
@@ -11321,10 +11333,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C26" t="n">
@@ -11353,10 +11365,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42307</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11385,10 +11397,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C28" t="n">
@@ -11417,10 +11429,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42494</v>
       </c>
       <c r="C29" t="n">
@@ -11449,10 +11461,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42585</v>
       </c>
       <c r="C30" t="n">
@@ -11481,10 +11493,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C31" t="n">
@@ -11513,10 +11525,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C32" t="n">
@@ -11545,10 +11557,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42858</v>
       </c>
       <c r="C33" t="n">
@@ -11577,10 +11589,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11609,10 +11621,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C35" t="n">
@@ -11641,10 +11653,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43151</v>
       </c>
       <c r="C36" t="n">
@@ -11673,10 +11685,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43215</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C37" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43306</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="C38" t="n">
@@ -11737,10 +11749,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43396</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43402</v>
       </c>
       <c r="C39" t="n">
@@ -11769,10 +11781,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="C40" t="n">
@@ -11801,10 +11813,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43578</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43584</v>
       </c>
       <c r="C41" t="n">
@@ -11833,10 +11845,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43669</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43676</v>
       </c>
       <c r="C42" t="n">
@@ -11865,10 +11877,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43760</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C43" t="n">
@@ -11897,10 +11909,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43886</v>
       </c>
       <c r="C44" t="n">
@@ -11929,10 +11941,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C45" t="n">
@@ -11961,10 +11973,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -11993,10 +12005,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C47" t="n">
@@ -12025,10 +12037,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C48" t="n">
@@ -12057,10 +12069,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -12089,10 +12101,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44414</v>
       </c>
       <c r="C50" t="n">
@@ -12121,10 +12133,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C51" t="n">
@@ -12153,10 +12165,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44615</v>
       </c>
       <c r="C52" t="n">
@@ -12185,10 +12197,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C53" t="n">
@@ -12217,10 +12229,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C54" t="n">
@@ -12249,10 +12261,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C55" t="n">
@@ -12281,10 +12293,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C56" t="n">
@@ -12313,10 +12325,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C57" t="n">
@@ -12345,10 +12357,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12377,10 +12389,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="C59" t="n">
@@ -12409,10 +12421,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C60" t="n">
@@ -12441,10 +12453,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45411</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12473,10 +12485,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45503</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12505,10 +12517,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45594</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="C63" t="n">
@@ -12537,10 +12549,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C64" t="n">
@@ -12569,10 +12581,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45776</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C65" t="n">
@@ -12601,10 +12613,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45867</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12633,10 +12645,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45960</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45964</v>
       </c>
       <c r="C67" t="n">
@@ -12665,10 +12677,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46070</v>
       </c>
       <c r="C68" t="n">
@@ -12697,10 +12709,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46141</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C69" t="n">
@@ -12729,10 +12741,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46233</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46237</v>
       </c>
       <c r="C70" t="n">
@@ -12779,12 +12791,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
